--- a/DataframeWilcoxon.xlsx
+++ b/DataframeWilcoxon.xlsx
@@ -71,13 +71,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -371,10 +380,10 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -382,10 +391,10 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>5.23</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>6.45</v>
       </c>
     </row>
@@ -393,10 +402,10 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>4.67</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>7.12</v>
       </c>
     </row>
@@ -404,10 +413,10 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>6.18</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>5.84</v>
       </c>
     </row>
@@ -415,10 +424,10 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>4.3899999999999997</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>7.56</v>
       </c>
     </row>
@@ -426,10 +435,10 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>5.72</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>8.2100000000000009</v>
       </c>
     </row>
@@ -437,10 +446,10 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>6.44</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>9.3699999999999992</v>
       </c>
     </row>
@@ -448,10 +457,10 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>3.15</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>4.62</v>
       </c>
     </row>
@@ -459,10 +468,10 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>7.83</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>5.29</v>
       </c>
     </row>
@@ -470,10 +479,10 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>8.5399999999999991</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>6.73</v>
       </c>
     </row>
@@ -481,10 +490,10 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>9.11</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>7.68</v>
       </c>
     </row>
@@ -492,10 +501,10 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>3.47</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>8.93</v>
       </c>
     </row>
@@ -503,10 +512,10 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="3">
         <v>5.26</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>7.41</v>
       </c>
     </row>
@@ -514,10 +523,10 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <v>4.88</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>8.17</v>
       </c>
     </row>
@@ -525,10 +534,10 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="3">
         <v>5.61</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>9.24</v>
       </c>
     </row>
@@ -536,10 +545,10 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="5">
         <v>7.34</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="5">
         <v>7.57</v>
       </c>
     </row>
@@ -547,10 +556,10 @@
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="5">
         <v>6.92</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="5">
         <v>8.36</v>
       </c>
     </row>
@@ -558,10 +567,10 @@
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="5">
         <v>5.14</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="5">
         <v>6.81</v>
       </c>
     </row>
@@ -569,21 +578,21 @@
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
-        <v>3.79</v>
-      </c>
-      <c r="C19" s="2">
-        <v>10.42</v>
+      <c r="B19" s="5">
+        <v>18.79</v>
+      </c>
+      <c r="C19" s="5">
+        <v>32.42</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="5">
         <v>4.5199999999999996</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="5">
         <v>8.65</v>
       </c>
     </row>
@@ -591,10 +600,10 @@
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="5">
         <v>5.37</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="5">
         <v>7.18</v>
       </c>
     </row>
@@ -602,21 +611,21 @@
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
-        <v>3.26</v>
-      </c>
-      <c r="C22" s="2">
-        <v>9.74</v>
+      <c r="B22" s="5">
+        <v>15.26</v>
+      </c>
+      <c r="C22" s="5">
+        <v>28.74</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="5">
         <v>6.49</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="5">
         <v>8.58</v>
       </c>
     </row>
@@ -624,10 +633,10 @@
       <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="5">
         <v>7.75</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="5">
         <v>7.33</v>
       </c>
     </row>
@@ -635,10 +644,10 @@
       <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="5">
         <v>4.16</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="5">
         <v>8.4700000000000006</v>
       </c>
     </row>
@@ -646,21 +655,21 @@
       <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
-        <v>7.58</v>
-      </c>
-      <c r="C26" s="2">
-        <v>9.15</v>
+      <c r="B26" s="5">
+        <v>22.58</v>
+      </c>
+      <c r="C26" s="5">
+        <v>35.15</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="5">
         <v>4.71</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="5">
         <v>8.89</v>
       </c>
     </row>
@@ -668,10 +677,10 @@
       <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="5">
         <v>5.95</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="5">
         <v>9.2799999999999994</v>
       </c>
     </row>
@@ -679,14 +688,15 @@
       <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="5">
         <v>3.42</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="5">
         <v>4.13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>